--- a/metadata/atacseq/todo/California Institute of Technology TMC (ATACseq).xlsx
+++ b/metadata/atacseq/todo/California Institute of Technology TMC (ATACseq).xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,7 +495,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10X Genomics; Visium Spatial Gene Expression Slide and Reagent Kit, 4 slides, 16 reactions; PN 1000184</t>
+          <t>10x Genomics; Chromium Next GEM Single Cell Fixed RNA Sample Preparation Kit, 16 rxns; PN 1000414</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -522,7 +522,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>Parse Biosciences; Evercode WT v2 Kit, 48 rxns; PN ECW02030</t>
+          <t>10X Genomics; Visium Spatial Gene Expression Slide and Reagent Kit, 4 slides, 16 reactions; PN 1000184</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -549,7 +549,7 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Single Cell 5' Kit v2, 16 rxns; PN 1000263</t>
+          <t>Parse Biosciences; Evercode WT v2 Kit, 48 rxns; PN ECW02030</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -576,7 +576,7 @@
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>10X Genomics; Visium Spatial for FFPE Gene Expression Kit, Human Transcriptome, 1 slides, 4 reactions; PN 1000338</t>
+          <t>10X Genomics; Chromium Next GEM Single Cell 5' Kit v2, 16 rxns; PN 1000263</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -598,7 +598,7 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Single Cell 3' Kit v3.1, 16 rxns; PN 1000268</t>
+          <t>10X Genomics; Visium Spatial for FFPE Gene Expression Kit, Human Transcriptome, 1 slides, 4 reactions; PN 1000338</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -620,7 +620,7 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>10x Genomics; Chromium Next GEM Single Cell ATAC Library &amp; Gel Bead Kit, 16 rxns; PN 1000175</t>
+          <t>10X Genomics; Chromium Next GEM Single Cell 3' Kit v3.1, 16 rxns; PN 1000268</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>10x Genomics; Library Construction Kit C, 16 rxns; PN 1000694</t>
+          <t>10x Genomics; Chromium Next GEM Single Cell ATAC Library &amp; Gel Bead Kit, 16 rxns; PN 1000175</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -654,7 +654,7 @@
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>10x Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Mouse Transcriptome, 6.5mm, 4 rxns; PN 1000521</t>
+          <t>10x Genomics; Library Construction Kit C, 16 rxns; PN 1000694</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Single Cell 3' HT Kit v3.1, 48 rxns; PN 1000348</t>
+          <t>10x Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Mouse Transcriptome, 6.5mm, 4 rxns; PN 1000521</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -688,7 +688,7 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Single Cell 3' GEM, Library &amp; Gel Bead Kit v3.1, 16 rxns; PN 1000121</t>
+          <t>10X Genomics; Chromium Next GEM Single Cell 3' HT Kit v3.1, 48 rxns; PN 1000348</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>10x Genomics; Library Construction Kit C, 4 rxns; PN 1000689</t>
+          <t>10X Genomics; Chromium Next GEM Single Cell 3' GEM, Library &amp; Gel Bead Kit v3.1, 16 rxns; PN 1000121</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -722,7 +722,7 @@
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>10X Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Human Transcriptome, 11 mm, 2 reactions; PN 1000522</t>
+          <t>10x Genomics; Library Construction Kit C, 4 rxns; PN 1000689</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Illumina; TruSeq Stranded mRNA Library Prep (48 samples); PN 20020594</t>
+          <t>10X Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Human Transcriptome, 11 mm, 2 reactions; PN 1000522</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>10X Genomics; Automated Library Construction Kit, 24 rxns; PN 1000428</t>
+          <t>Illumina; TruSeq Stranded mRNA Library Prep (48 samples); PN 20020594</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>New England BioLabs; NEBNext Ultra II RNA Library Prep Kit for Illumina; PN E7770</t>
+          <t>10X Genomics; Automated Library Construction Kit, 24 rxns; PN 1000428</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -790,7 +790,7 @@
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Automated Single Cell 5' Kit v2, 24 rxns; PN 1000290</t>
+          <t>New England BioLabs; NEBNext Ultra II RNA Library Prep Kit for Illumina; PN E7770</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -807,7 +807,7 @@
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>10X Genomics; Visium Spatial Gene Expression Slide and Reagent Kit, 1 slides, 4 reactions; PN 1000187</t>
+          <t>10X Genomics; Chromium Next GEM Automated Single Cell 5' Kit v2, 24 rxns; PN 1000290</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -824,7 +824,7 @@
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>10x Genomics; Chromium GEM-X Single Cell 5' Kit v3, 16 rxns; PN 1000699</t>
+          <t>10X Genomics; Visium Spatial Gene Expression Slide and Reagent Kit, 1 slides, 4 reactions; PN 1000187</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -836,7 +836,7 @@
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>10x Genomics; Chromium Single Cell ATAC Library &amp; Gel Bead Kit, 16 rxns; PN 1000110</t>
+          <t>10x Genomics; Chromium GEM-X Single Cell 5' Kit v3, 16 rxns; PN 1000699</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -848,7 +848,7 @@
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>10x Genomics; Library Construction Kit, 16 rxns; PN 1000190</t>
+          <t>10x Genomics; Chromium Single Cell ATAC Library &amp; Gel Bead Kit, 16 rxns; PN 1000110</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -860,7 +860,7 @@
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>Parse Biosciences; Evercode WT Mini v2 Kit, 12 rxns; PN ECW02010</t>
+          <t>10x Genomics; Library Construction Kit, 16 rxns; PN 1000190</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>10x Genomics; Chromium Next GEM Single Cell 5' HT Kit v2, 48 rxns; PN 1000356</t>
+          <t>Parse Biosciences; Evercode WT Mini v2 Kit, 12 rxns; PN ECW02010</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -884,7 +884,7 @@
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>Illumina; TruSeq Stranded mRNA Library Prep (96 samples); PN 20020595</t>
+          <t>10x Genomics; Chromium Next GEM Single Cell 5' HT Kit v2, 48 rxns; PN 1000356</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -896,7 +896,7 @@
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Single Cell 5' Kit v2, 4 rxns; PN 1000265</t>
+          <t>Illumina; TruSeq Stranded mRNA Library Prep (96 samples); PN 20020595</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -908,7 +908,7 @@
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium NextGem Single Cell Multiome ATAC + Gene Expression Reagent Bundle, 4 rxn; PN 1000285</t>
+          <t>10X Genomics; Chromium Next GEM Single Cell 5' Kit v2, 4 rxns; PN 1000265</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -920,7 +920,7 @@
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Single Cell Fixed RNA Hybridization &amp; Library Kit, 4 rxns; PN 1000415</t>
+          <t>10X Genomics; Chromium NextGem Single Cell Multiome ATAC + Gene Expression Reagent Bundle, 4 rxn; PN 1000285</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>10X Genomics; Chromium Next GEM Single Cell Fixed RNA Hybridization &amp; Library Kit, 4 rxns; PN 1000415</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -944,54 +944,75 @@
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Single Cell 3' GEM, Library &amp; Gel Bead Kit v3, 4 rxns; PN 1000092</t>
+          <t>Custom</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>10x Genomics; Chromium Single Cell 3ʹ GEM, Library &amp; Gel Bead Kit v3, 16 rxns; PN 1000075</t>
+          <t>10X Genomics; Chromium Single Cell 3' GEM, Library &amp; Gel Bead Kit v3, 4 rxns; PN 1000092</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Single Cell 3' Library &amp; Gel Bead Kit, 4 rxns; PN 120267</t>
+          <t>10x Genomics; Chromium Single Cell 3ʹ GEM, Library &amp; Gel Bead Kit v3, 16 rxns; PN 1000075</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>10X Genomics; Visium Spatial for FFPE Gene Expression Kit, Mouse Transcriptome, 4 rxns; PN 1000339</t>
+          <t>10X Genomics; Chromium Single Cell 3' Library &amp; Gel Bead Kit, 4 rxns; PN 120267</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium NextGem Single Cell Multiome ATAC + Gene Expression Reagent Bundle, 16 rxn; PN 1000283</t>
+          <t>10X Genomics; Visium Spatial for FFPE Gene Expression Kit, Mouse Transcriptome, 4 rxns; PN 1000339</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Single Cell 3' Kit v3.1, 4 rxns; PN 1000269</t>
+          <t>10X Genomics; Chromium NextGem Single Cell Multiome ATAC + Gene Expression Reagent Bundle, 16 rxn; PN 1000283</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>10x Genomics; Chromium Next GEM Single Cell 5' HT Kit v2, 8 rxns; PN 1000374</t>
+          <t>Epigenome Technologies; Multiplex Droplet Paired-Tag 16 Reaction Kit; PN MDP16101</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
+        <is>
+          <t>10X Genomics; Chromium Next GEM Single Cell 3' Kit v3.1, 4 rxns; PN 1000269</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>10x Genomics; GEM-X Flex GEM &amp; Library Kit, 4 rxns; PN 1000782</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>10x Genomics; Chromium Next GEM Single Cell 5' HT Kit v2, 8 rxns; PN 1000374</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
         <is>
           <t>10X Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Human Transcriptome, 6.5mm, 4 reactions; PN 1000520</t>
         </is>
@@ -1051,7 +1072,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -1093,7 +1114,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -1135,7 +1156,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -1177,7 +1198,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1219,7 +1240,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1261,7 +1282,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1303,7 +1324,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1345,7 +1366,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1387,7 +1408,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1429,7 +1450,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1471,7 +1492,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1513,7 +1534,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1555,7 +1576,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1597,7 +1618,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1639,7 +1660,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Illumina; NextSeq 500 Reagent Kit</t>
+          <t>Nextseq500</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1681,7 +1702,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1723,7 +1744,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1765,7 +1786,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1807,7 +1828,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1849,7 +1870,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1891,7 +1912,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1933,7 +1954,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1975,7 +1996,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -2017,7 +2038,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -2059,7 +2080,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -2101,7 +2122,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -2143,7 +2164,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -2185,7 +2206,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -2227,7 +2248,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -2269,7 +2290,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -2311,7 +2332,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -2353,7 +2374,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -2395,7 +2416,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2437,7 +2458,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -2479,7 +2500,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -2521,7 +2542,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -2563,7 +2584,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Illumina; NovaSeq 6000 Reagent Kit</t>
+          <t>NovaSeq6000</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -7990,7 +8011,7 @@
       <formula1>_validation_data!$A$1:$A$3</formula1>
     </dataValidation>
     <dataValidation sqref="C4 C12 C20 C28 C36 C44 C52 C60 C68 C76 C84 C92 C100 C108 C117 C125 C133 C141 C149 C157 C165 C173 C181 C189 C197 C205 C213 C221 C229 C237 C245 C253 C261 C269 C277 C285 C293" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
-      <formula1>_validation_data!$B$1:$B$37</formula1>
+      <formula1>_validation_data!$B$1:$B$40</formula1>
     </dataValidation>
     <dataValidation sqref="C5 C13 C21 C29 C37 C45 C53 C61 C69 C77 C85 C93 C101 C109 C118 C126 C134 C142 C150 C158 C166 C174 C182 C190 C198 C206 C214 C222 C230 C238 C246 C254 C262 C270 C278 C286 C294" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
       <formula1>_validation_data!$C$1:$C$19</formula1>
